--- a/Aplicativos/pendencias/bd_saida/Loja 004.xlsx
+++ b/Aplicativos/pendencias/bd_saida/Loja 004.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,26 +461,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGUA MIN FLORESTA 500ML C GAS</t>
+          <t>FLANELA ALG PANOSUL AMAR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15308</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -488,35 +488,35 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>461</v>
+        <v>42</v>
       </c>
       <c r="H2" t="n">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G ABACAXI HORTELA</t>
+          <t>PANO PANOSUL DUPLO 100 ALGODAO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34351</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -533,26 +533,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACHOC LIQ ELEGE 1L BOB ESPONJA</t>
+          <t>PANO PANOSUL MEDIO C BAR 45X65 R24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -560,31 +560,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACHOC TODDY PT 750G ORIGINAL MAIS ECONOMIC</t>
+          <t>PANO PANOSUL MEDIO ESTAMP 45X65 R23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -596,35 +596,35 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>21557</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACUCAR DEMERARA GASPARIN 1K</t>
+          <t>PANO PTO PANOSUL COLOR C EST</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -632,35 +632,35 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21559</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AGUA MIN AGUA DA PEDRA PET 2L C GAS</t>
+          <t>PANO SARJA PANOSUL 45X75CM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -668,35 +668,35 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AGUA MINERAL CRYSTAL S G PET 1 5L</t>
+          <t>SACO PANOSUL 60X68CM XADREZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -704,35 +704,35 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>225</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12294</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AGUA TONICA QUININO ZERO 1 5ML</t>
+          <t>SC PANOSUL ALVEJADO 48X63CM R 14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -740,35 +740,35 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMAC YPE CONC 500ML PINK</t>
+          <t>SC PANOSUL SUPER ALV BCO 39X65 R 10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BALAO LISO 6 5 C 30 ROSA</t>
+          <t>TOAL ROSTO FAVO 40X60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -812,35 +812,35 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>24984</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BALAO LISO 6 5 C 30 SORT</t>
+          <t>TOAL SOCIAL PANOSUL 23X38CM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -848,35 +848,35 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>780</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BALAO ZERINHO C 100 SORT</t>
+          <t>TOALHINHA KIDS 25X25CM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -884,35 +884,35 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BEB VIT BALY KIDS LT 220ML TUTTI FRUTI</t>
+          <t>ABS C ABAS DIA NOITE 32 UN SUAVE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -929,26 +929,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BEBIDA 3 CORACOES POWER WHEY 250ML COOKIE</t>
+          <t>AGUA SANIT IMPERIAL 2L</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>39225</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -956,35 +956,35 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BEBIDA ADES PESSEG TP 200ML</t>
+          <t>AGUA SANIT IMPERIAL 5L</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>39225</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -992,35 +992,35 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BEBIDA PARMALAT WHEY 250ML BAUNILHA</t>
+          <t>AGUA SANIT Q BOA 1L</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -1037,26 +1037,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BEBIDA PARMALAT WHEY 250ML CAPPUCCINO</t>
+          <t>AGUA SANIT YPE 2L</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -1073,26 +1073,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>936</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BEBIDA PARMALAT WHEY 250ML COCO</t>
+          <t>AZEITE DENDE TRISANTI 200ML</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -1109,26 +1109,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BEBIDA SCHWEPPES GIN TONICA</t>
+          <t>BALA DORI GELATINA 13G AMORA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H20" t="n">
         <v>2</v>
@@ -1145,26 +1145,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIFINHO PETISCAO TABLETE 60G CAR</t>
+          <t>BALA DORI GELATINA 13G BANANA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1172,35 +1172,35 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BR KIDIVERTIDO SORT REF 1999</t>
+          <t>BALA DORI GELATINA 13G BOCA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1208,35 +1208,35 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CAD ESPI CD 10X1 160FLS SWEETNESS</t>
+          <t>BALA DORI GELATINA 13G MINHOCA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1244,71 +1244,71 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAD ESPI CD 1X1 80FLS SWEETNESS</t>
+          <t>BARRA CEREAL RITTER 22G CAST PARA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>4</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>108</v>
-      </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>36312</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CANECA VD LISA C3 250ML TRASPARENTE</t>
+          <t>BARRA CEREAL RITTER 25G AVELA CAST CHOC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1316,35 +1316,35 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>351</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CARV VEG CHUR NA BRASA 3K</t>
+          <t>CERV BRAHMA CHOPP LT 350ML ZERO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1352,35 +1352,35 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>599</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CARVAO VEG CHURRASCO NA BRASA 5KG</t>
+          <t>CHICLE FREEGELLS GUM 8G CANELA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1388,35 +1388,35 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H27" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL BEATS LT 269ML GIN TONICA</t>
+          <t>CHICLE FREEGELLS GUM 8G MELANCIA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -1433,26 +1433,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CESTA BASICA PEQ</t>
+          <t>CHICLE FREEGELLS GUM 8G MORANGO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1460,35 +1460,35 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>616</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHA ICE TEA LEAO PET 1 5L LIMAO ZERO</t>
+          <t>CHICLE FREEGELLS GUM 8G ORIGINAL MINT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1496,35 +1496,35 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CHA LEAO MATTE PET 1 5L NATURAL</t>
+          <t>CHICLE FREEGELLS GUM 8G TUTTI FRUTTI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H31" t="n">
         <v>2</v>
@@ -1541,26 +1541,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CHUP CEFISA SIL ORT T2</t>
+          <t>CHOC KINDER BUENO WHITE 39G</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>31179</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -1577,26 +1577,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COBER COBERTOP M AMARG GOTAS 1 01KG</t>
+          <t>COMEDOURO PET MELAMINA DUPLO 1 2L</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>33061</t>
+          <t>39896</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1604,35 +1604,35 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>165</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>36599</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>COLA THREE BOND SUPER 2G</t>
+          <t>CORDA VARAL TORCIDA PET 11LC00318 10MT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1640,35 +1640,35 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COND SEDA 325ML LISO PERFEITO</t>
+          <t>CR DEN COLGATE 90G MPA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>31179</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1676,35 +1676,35 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>144</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CONHAQ PRESIDENTE 900ML</t>
+          <t>CR DEN COLGATE WHITENING 180G</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
         <v>2</v>
@@ -1721,26 +1721,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CORANTE TINGECOR 40G GUARANY MARINHO N16</t>
+          <t>CR DENTAL TANDY 50G MORANGO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1748,35 +1748,35 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>34823</t>
+          <t>36397</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CP STITCH C CANUDO</t>
+          <t>CREME DENT COLGATE LUM COLOR 70G</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -1793,26 +1793,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>17163</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CR DEN COLGATE 90G NAT EXT CARVAO</t>
+          <t>DESINF AQUAFAST 2L MARINE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
@@ -1829,26 +1829,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DESINF AQUAFAST 2L MARINE</t>
+          <t>DESINF GOTA LIMPA 5L EUCALIPTO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="H40" t="n">
         <v>1</v>
@@ -1865,26 +1865,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DOCE LEITE STA CLARA PT 400G</t>
+          <t>DESINF GOTA LIMPA 5L PINHO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="H41" t="n">
         <v>1</v>
@@ -1901,22 +1901,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>35020</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DUCHA GORDUCHA ZAFONEL 4T 220V</t>
+          <t>DESO AERO AXE 200ML APO VET E MANDA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -1937,26 +1937,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DUETO FUGINI SH 170G ERVILHA MILHO</t>
+          <t>DESOD SANIT GOTA LIMPA 25G LAVANDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>31179</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1964,35 +1964,35 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>357</v>
+        <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EMB PRATICA GABOARDI 2KG</t>
+          <t>DET LIQ AQUAFAST LAV RAP CLEAN 1 5L</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2000,35 +2000,35 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EMB PRATICA GABOARDI 3KG</t>
+          <t>DET LIQ GOTA LIMPA 500ML LIMAO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2036,35 +2036,35 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EMB PRATICA GABOARDI 5KG</t>
+          <t>DET LIQ GOTA LIMPA 500ML MACA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2072,31 +2072,31 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>18</v>
+        <v>234</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EMB ROYALPACK MULTI FREEZER 2KG</t>
+          <t>DET LIQ GOTA LIMPA 500ML MARINE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -2108,35 +2108,35 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ENERG BALY LT 473ML MANGA</t>
+          <t>DET LIQ GOTA LIMPA 500ML NEUTRO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2144,35 +2144,35 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>243</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ENERG BALY PET 2L MELANCIA</t>
+          <t>DET LIQ ULTRA 5L CLASS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>5</v>
+        <v>161</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
@@ -2189,26 +2189,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ENERG ELEV LT 473 ML FRUT TROPICAIS</t>
+          <t>DET PO GIRANDO SOL ROSA SH 400G</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2216,35 +2216,35 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ENERG MONSTER LT 473ML MANGO LOCO</t>
+          <t>DROPS FREEGELLS 27 6G CEREJA CHOC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>33910</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2252,35 +2252,35 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>31</v>
+        <v>1053</v>
       </c>
       <c r="H51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ENERG MONSTER LT 473ML ULTRA</t>
+          <t>DROPS FREEGELLS 27 9G CEREJA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>33910</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2288,35 +2288,35 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ENERG RED BULL LT 250ML</t>
+          <t>DROPS FREEGELLS 27 9G FRESH MELAO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2324,35 +2324,35 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ENERG RED BULL LT 250ML MORANGO PESSEGO</t>
+          <t>DROPS FREEGELLS 27 9G MENTA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2360,35 +2360,35 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>33730</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ENERG RED BULL LT 250ML ZERO</t>
+          <t>DROPS FREEGELLS 27 9G MORANGO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
@@ -2405,22 +2405,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EPI LUVA MULTITATO 9 G</t>
+          <t>DROPS FREEGELLS 27 9G VIT C CITRUS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2432,35 +2432,35 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ERVA MATE PONCHE VERDE 500G MOIDA GROSSA</t>
+          <t>FRALDA DESC MILI LOVECARE RN 18UN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="H57" t="n">
         <v>1</v>
@@ -2477,26 +2477,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ERVILHA SERRA URUGUAI PARTIDA 500G</t>
+          <t>GUARD NATUPEL PREMIUM 20X20 50FLS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2504,35 +2504,35 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>170</v>
+        <v>109</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ERVILHA YOKI PARTIDA 400GR</t>
+          <t>LEITE LV EDGE ELEGE 1L INTEGRAL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2540,35 +2540,35 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>21</v>
+        <v>1435</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ESFREGAO ACO DIVINOX 10G</t>
+          <t>LIMP UAU LV1L PG800ML FLORES VERMELHA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
         <v>1</v>
@@ -2585,26 +2585,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ESP ACO ASSOLAN C 08</t>
+          <t>LIMP UAU LV1L PG800ML LAVANDA CONFORT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2612,35 +2612,35 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>131</v>
+        <v>16</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>18268</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ESPETIN GABOARDI BAMBU P CHUR C 50</t>
+          <t>LUVA CONF LATEX G AMARELA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2648,35 +2648,35 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ESPETINHO GABOARDI BAMBU EXT</t>
+          <t>MAC CUP NOODLES 68PARMEGIANA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>232</v>
+        <v>4</v>
       </c>
       <c r="H63" t="n">
         <v>2</v>
@@ -2693,26 +2693,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>31452</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FACA TRAMONTINA CHURRASCO 4 LEME PRETA</t>
+          <t>MAC INST NISSIN 85G COSTELA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H64" t="n">
         <v>1</v>
@@ -2729,26 +2729,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FACA TRAMONTINA CHURRASCO 4 LEME VERMELHA</t>
+          <t>MAC INST NISSIN 85G LEGUMES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2756,35 +2756,35 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>33449</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FEIJAO PRETO CALDO OURO 500G</t>
+          <t>MAC INST NISSIN 85G PIC CALABRESA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2792,35 +2792,35 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>513</v>
+        <v>18</v>
       </c>
       <c r="H66" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>18516</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FILME UTILFILME 15M</t>
+          <t>MAC INST NISSIN 85G PICANHA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2828,35 +2828,35 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FOSFORO GABOARDI 10UN</t>
+          <t>MAC INST NISSIN CHICO BENTO 75G GAL C TOM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2864,35 +2864,35 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>20339</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FOSFORO PARANA ECO 10X40UN</t>
+          <t>MAC INST NISSIN CHICO BENTO 75G SUAV MILH MA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
@@ -2909,26 +2909,26 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>18850</t>
+          <t>20365</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FUMO TUPA 28G</t>
+          <t>MAC INST NISSIN TALH 99G FGO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2936,35 +2936,35 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>604</v>
+        <v>5</v>
       </c>
       <c r="H70" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>20374</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FUMO VITORIA 28G</t>
+          <t>MAC INST YAKISSOBA UFO 97G CARNE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H71" t="n">
         <v>1</v>
@@ -2981,26 +2981,26 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GARFO TRAMONTINA MESA INOX LEME PRETO</t>
+          <t>MAC INST YAKISSOBA UFO 97G GAL CAIP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H72" t="n">
         <v>1</v>
@@ -3017,22 +3017,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GATORADE ZERO 350ML LARANJA LIMA</t>
+          <t>MAC INST YAKISSOBA UFO 97G LEGUMES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -3044,35 +3044,35 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEL DENT SORRISO FRESH 90G HORTELA</t>
+          <t>MACARRAO CUP NOODLES 69G NACHO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3080,35 +3080,35 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GELATINA NEILAR 20G PESSEGO</t>
+          <t>MACARRAO CUP NOODLES 70G YAKISSOBA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>33910</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3116,35 +3116,35 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GIN ROCKS 1L SICILIAN LEMON</t>
+          <t>MACARRAO CUP NOODLES 72G TERIYAKI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
         <v>2</v>
@@ -3161,26 +3161,26 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>19271</t>
+          <t>20317</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GUARD NATUPEL PREMIUM 20X20 50FLS</t>
+          <t>MACARRAO INST GERMANI 63G GALINHA CAIPIRA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>109</v>
+        <v>460</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
@@ -3197,26 +3197,26 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>INCENSO FLUTE C 8 SAL GROSSO</t>
+          <t>MACARRAO INST NISSIN 500G YAKISSOBA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="H78" t="n">
         <v>2</v>
@@ -3233,26 +3233,26 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>INSET MAT INSET MULTI PROMO 360ML INSETICIDA</t>
+          <t>MACARRAO INST NISSIN 85G CAR PICANTE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
@@ -3269,26 +3269,26 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LAMP TRAM LED ALTA PTNCIA 20W 6500K</t>
+          <t>MAS CAS PASTAMIA C OVOS 400G TALHARIM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3296,35 +3296,35 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H80" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>20609</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LENHA P FOGAO 10K</t>
+          <t>MAS ESPAG ISABELA SEMOLA 400G</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>38827</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>11</v>
+        <v>241</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
@@ -3341,26 +3341,26 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20278</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LUVA CONF LATEX M AMARELA</t>
+          <t>MAS MACARRAO BOM GOSTO SEMOLA 400G</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>38827</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
@@ -3377,26 +3377,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LUVA CONF LATEX P AMARELA</t>
+          <t>MASSA C OVOS DOMELLY 500G ESPAGUETE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3404,35 +3404,35 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20282</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LUVA DANNY SILVER GRIP M AZUL</t>
+          <t>MASSA C OVOS ISABELA 500G ESPAGUETE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3440,35 +3440,35 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="H84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20391</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MAIONESE LIZA CASEIRA 450G</t>
+          <t>MASSA C OVOS NORDESTE 500G ESPAGUETE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>31983</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3476,35 +3476,35 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="H85" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MAS CAS PASTAMIA C OVOS 400G FETTUCCINE</t>
+          <t>MASSA C OVOS ORQUIDEA 500G CONCHA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="H86" t="n">
         <v>1</v>
@@ -3521,26 +3521,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MASSA C OVOS NORDESTE 500G PARAFUSO</t>
+          <t>MILHO PIPOCA BELLA DICA 400GR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="H87" t="n">
         <v>1</v>
@@ -3557,26 +3557,26 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OLEO IPIRANGA MOTO PROT 20W50 SL</t>
+          <t>ODORIZ AMAZONIA AROM 270ML ALFAZEMA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H88" t="n">
         <v>2</v>
@@ -3593,26 +3593,26 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PALITO DENTE PARANA MADEIRA 100UN</t>
+          <t>OLEO IPIRANGA 2T MOTO 200ML</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>40335</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3620,35 +3620,35 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H89" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PAPEL HIG DOBLE COMP FD 16UN C 30M</t>
+          <t>PAPEL HIG ATUALLE 20M FLA DP 12UN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3656,35 +3656,35 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21661</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PAPEL HIG DOBLE FD 4 UN C 30M</t>
+          <t>PAPEL HIG COMFORT FLA DPL 30M 18 UN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
@@ -3701,26 +3701,26 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PAPEL HIG DUETTO 4 UN DE 30M NEUTRO</t>
+          <t>PAPEL HIG DUETTO FD 12 UN DE 30M NEUTRO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3728,35 +3728,35 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PAPEL HIG DUETTO 4 UN DE 30M PERFUMADO</t>
+          <t>PAPEL HIG MILI PERFUM FLA SPL 60M 4UN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>32259</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>47</v>
+        <v>155</v>
       </c>
       <c r="H93" t="n">
         <v>1</v>
@@ -3773,26 +3773,26 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PAPEL HIG MILI NEUTRO FHA DPL 30M 12UN</t>
+          <t>PAPEL HIG NATUPEL PREM FS 30M C 4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>85</v>
+        <v>901</v>
       </c>
       <c r="H94" t="n">
         <v>2</v>
@@ -3809,26 +3809,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>21685</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PAPEL HIG MILI NEUTRO FLA SPL 100M 12UN</t>
+          <t>PAPEL HIG NESS FD 30M</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3836,35 +3836,35 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>21686</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PAPEL HIG MILI NEUTRO FLA SPL 60M 4UN</t>
+          <t>PAPEL HIG SIRIUS PREMIER FD 20M C12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3872,35 +3872,35 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PAPEL HIG MILI PERFUM FLA DPL 30M 12UN</t>
+          <t>PAPEL HIG STYLUS FD 24 UN DE 20M NEUTRO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="H97" t="n">
         <v>2</v>
@@ -3917,26 +3917,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PAPEL HIG NATUPEL FD 20M C 12</t>
+          <t>PAPEL HIG SULINO NEUTRO FS FD 12UN DE 60M</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3944,35 +3944,35 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>363</v>
+        <v>7</v>
       </c>
       <c r="H98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PAPEL HIG NATUPEL PREM FS 60M C 4</t>
+          <t>PAST DOCILE MINTY 14G LAR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>32259</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3980,35 +3980,35 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>21694</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PAPEL HIG NESS FD 20M 12UN</t>
+          <t>PAST DOCILE MINTY 14G MOR</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4016,35 +4016,35 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>21706</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PAPEL HIG PLUSH COMPACTO FD 20M 12U</t>
+          <t>PAST DOCILE MINTY 14G TUTTI FRUTTI</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4052,35 +4052,35 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PAPEL HIG SIRIUS PREMIER FD 30M C32</t>
+          <t>PAST DOCILE ROLLY MINTY 29G EXTRA FORTE</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4088,35 +4088,35 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>731</v>
+        <v>5</v>
       </c>
       <c r="H102" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PAPEL HIG STYLUS 12 UN DE20M NEUTRO</t>
+          <t>PAST DOCILE ROLLY MINTY 29G FRUIT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>32259</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6</v>
+        <v>360</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4124,35 +4124,35 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PAPEL HIG SULINO NEUTRO FS FD 12UN DE 60M</t>
+          <t>PRENDEDOR ROUPA GABOARDI GIG12UN</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H104" t="n">
         <v>1</v>
@@ -4169,26 +4169,26 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>22633</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PAPEL HIG SULINO NEUTRO FS FD 4UN DE 60M</t>
+          <t>QJO RAL KIFORMAGGIO TRAD 40G</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4196,35 +4196,35 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21700</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PAPEL HIG SULINO NEUTRO FS FD C 4UN DE 30M</t>
+          <t>RAC CANISTER ALMONDEGA 7K</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -4232,35 +4232,35 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>7</v>
+        <v>108</v>
       </c>
       <c r="H106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PAPEL TOALHA MAXIM STYLUS 2RL 50UN</t>
+          <t>RACAO PEDIGREE HIGH PROT SH 85G CARNE FGO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4268,35 +4268,35 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>33872</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PAPEL TOALHA MILI 2UN</t>
+          <t>REFRE HAPPY TP 200ML PESSEGO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>32259</t>
+          <t>39954</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="H108" t="n">
         <v>2</v>
@@ -4313,26 +4313,26 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>21734</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PAPEL TOALHA NATUREZA FD 2UN</t>
+          <t>SAB FARNESE 180G LAVANDA MENTA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4340,35 +4340,35 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="H109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>36301</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>POMADA MASSAG BIO FISIOFORT 150ML</t>
+          <t>SAB MARAN SUAVE 80G ERVA DOCE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>31179</t>
+          <t>39701</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4376,35 +4376,35 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PTO RASO FORFEST 15CM RSA 10UN</t>
+          <t>SAB MARAN SUAVE 80G ROSAS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>39701</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -4412,35 +4412,35 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>22687</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RAC CANISTER ALMONDEGA 7K</t>
+          <t>SC LIXO ALMOF CASAFORT 100L C 5</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4448,35 +4448,35 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="H112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>33870</t>
+          <t>24104</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>REFRE HAPPY TP 200ML MORANGO</t>
+          <t>SC LIXO PRO LIXO ROLINHO 30L C 10</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>33910</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -4484,35 +4484,35 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G ABACAXI</t>
+          <t>SC LIXO ROL CASAFORT 100L C 10 AZ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4520,35 +4520,35 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="H114" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24113</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G ABACAXI HORTELA</t>
+          <t>SC LIXO ROL CASAFORT 15L C 40 AZ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -4556,35 +4556,35 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H115" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24118</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G GUARANA</t>
+          <t>SC LIXO ROL CASAFORT 50L C 20 PT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4592,35 +4592,35 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="H116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G LARANJA</t>
+          <t>SC LIXO ROL DOBRASIL 30L C 20 AZ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -4628,35 +4628,35 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>157</v>
+        <v>3</v>
       </c>
       <c r="H117" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G LARANJA BAHIA</t>
+          <t>SC LIXO ROL DOBRASIL 50L C 20 AZ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -4664,35 +4664,35 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="H118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>24313</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G LIMAO</t>
+          <t>SH DARLING CERAMIDAS 650ML</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4700,35 +4700,35 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H119" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G LIMONADA SUICA</t>
+          <t>SH HEAD SHOULDERS 200ML MENTHOL REFRE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4736,35 +4736,35 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>514</v>
+        <v>10</v>
       </c>
       <c r="H120" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G MANGA</t>
+          <t>TEMP AMACIANTE CARNE MAGGI 120G</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>38827</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4772,35 +4772,35 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G MARACUJA</t>
+          <t>TEMP COMPLETO NEILAR 250G C PIMENTA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -4808,35 +4808,35 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G MORANGO</t>
+          <t>TEMP COMPLETO ODERICH 300G S PIMENTA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -4844,35 +4844,35 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="H123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G TANGERINA</t>
+          <t>TEMP MAGGI TEMPERO E SABOR 50G AVES</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>38827</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4880,35 +4880,35 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>REFRE PO TRINK 15G UVA</t>
+          <t>TEMP MAGGI TEMPERO E SABOR 50G CARNES</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>38827</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -4916,31 +4916,31 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="H125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>25114</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>REFRIG ANTARCTICA GUAR LT 350ML ZR</t>
+          <t>VAS TROPICAL M USO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4952,35 +4952,35 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>25105</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>REFRIG COCA COLA E SPRITE 2L</t>
+          <t>VASSOURA DONA DA CASA C CABO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -4988,35 +4988,35 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>220</v>
+        <v>770</v>
       </c>
       <c r="H127" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>REFRIG COCA COLA LT 220ML S ACUCAR</t>
+          <t>VELA SANDERO T 7 DIAS VERM</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -5024,35 +5024,35 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="H128" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>REFRIG COCA COLA ZERO LT 310ML C6</t>
+          <t>VINAGRE ALCOOL KOLLER 750ML</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -5060,35 +5060,35 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="H129" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>REFRIG FANTA LAR ZERO PET 2L</t>
+          <t>VINAGRE ALCOOL ROSINA 750ML</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5105,26 +5105,26 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>REFRIG FANTA LARANJA LT 350ML</t>
+          <t>VINAGRE VINHO KOLLER 500ML TINTO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -5132,35 +5132,35 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>415</v>
+        <v>29</v>
       </c>
       <c r="H131" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>REFRIG FANTA LT 220ML</t>
+          <t>VINAGRE VINHO ROSINA 750ML TINTO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -5168,2313 +5168,9 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="H132" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>REFRIG FANTA PET 200ML LARANJA</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>12</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
-        <v>267</v>
-      </c>
-      <c r="H133" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>REFRIG SODA LIMONADA PET 2L</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>34479</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>8</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G134" t="n">
-        <v>22</v>
-      </c>
-      <c r="H134" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>REFRIG SPRITE LT 350ML</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
-        <v>6</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
-        <v>145</v>
-      </c>
-      <c r="H135" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>REFRIG SUKITA PET 200ML</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>34479</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
-        <v>12</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
-        <v>29</v>
-      </c>
-      <c r="H136" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>REPOSITOR ENGOV AFTER 250ML BERRY VIBES</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>33234</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
-        <v>6</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
-        <v>3</v>
-      </c>
-      <c r="H137" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>22960</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>ROLO ALUM GRILL 30X4M</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>36248</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
-        <v>25</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>39</v>
-      </c>
-      <c r="H138" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>22961</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>ROLO ALUM GRILL 45X4M</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>36248</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
-        <v>35</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>14</v>
-      </c>
-      <c r="H139" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>22962</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>ROLO ALUM GRILL 45X7 5M</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>36248</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>35</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
-        <v>9</v>
-      </c>
-      <c r="H140" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>22963</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>ROLO ALUM GRILL 7 5MX30CM</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>36248</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>25</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
-        <v>31</v>
-      </c>
-      <c r="H141" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>34772</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>SAB GRANADO ENXOFRE 90G</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>32918</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>12</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
-        <v>19</v>
-      </c>
-      <c r="H142" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>23052</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>SAB LIQ HEDERA 370ML FTA VRM</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>33234</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>12</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G143" t="n">
-        <v>3</v>
-      </c>
-      <c r="H143" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>34979</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>SAB MARAN SUAVE 80G AMENDOAS</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
-        <v>100</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G144" t="n">
-        <v>69</v>
-      </c>
-      <c r="H144" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>34977</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>SAB MARAN SUAVE 80G PESSEGO</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
-        <v>100</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G145" t="n">
-        <v>79</v>
-      </c>
-      <c r="H145" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>8018</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>SACO PANOSUL 60X68CM XADREZ</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>25</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G146" t="n">
-        <v>3</v>
-      </c>
-      <c r="H146" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>24061</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>SAPONACEO CREM FONT 250ML CITRUS</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>33157</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>12</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G147" t="n">
-        <v>2</v>
-      </c>
-      <c r="H147" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>24084</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>SC LIXO ALMOF CASAFORT 100L C 5</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>35662</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>50</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G148" t="n">
-        <v>16</v>
-      </c>
-      <c r="H148" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>24096</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>SC LIXO PRO LIXO ROLAO 100L C 25</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>35583</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>12</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G149" t="n">
-        <v>37</v>
-      </c>
-      <c r="H149" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>24098</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>SC LIXO PRO LIXO ROLAO 15L C 100</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>35583</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
-        <v>12</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G150" t="n">
-        <v>12</v>
-      </c>
-      <c r="H150" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>24099</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>SC LIXO PRO LIXO ROLAO 200L C 7</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>35583</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
-        <v>12</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G151" t="n">
-        <v>8</v>
-      </c>
-      <c r="H151" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>24100</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>SC LIXO PRO LIXO ROLAO 30L C 50</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>35583</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>12</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G152" t="n">
-        <v>13</v>
-      </c>
-      <c r="H152" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>24102</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>SC LIXO PRO LIXO ROLINHO 100L C 5</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>35583</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>25</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G153" t="n">
-        <v>28</v>
-      </c>
-      <c r="H153" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>24105</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>SC LIXO PRO LIXO ROLINHO 50L C 10</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>35583</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>25</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G154" t="n">
-        <v>17</v>
-      </c>
-      <c r="H154" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>24108</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>SC LIXO ROL CASAFORT 100L C 10 AZ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>35662</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>25</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G155" t="n">
-        <v>47</v>
-      </c>
-      <c r="H155" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>24109</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>SC LIXO ROL CASAFORT 100L C 25</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>35662</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>15</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G156" t="n">
-        <v>25</v>
-      </c>
-      <c r="H156" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>24113</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>SC LIXO ROL CASAFORT 15L C 40 AZ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>35662</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>25</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G157" t="n">
-        <v>21</v>
-      </c>
-      <c r="H157" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>24115</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>SC LIXO ROL CASAFORT 30L C 20 PT</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>35662</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>25</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G158" t="n">
-        <v>33</v>
-      </c>
-      <c r="H158" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>24118</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>SC LIXO ROL CASAFORT 50L C 20 PT</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>35662</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>25</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G159" t="n">
-        <v>24</v>
-      </c>
-      <c r="H159" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>24126</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>SC LIXO ROL DOBRASIL 50L C 20 AZ</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>35662</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>25</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G160" t="n">
-        <v>11</v>
-      </c>
-      <c r="H160" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>8408</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>SH VINI LADY 325ML PRETO ABSOLUTO</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>31179</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>12</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G161" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>24332</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>SHAMPOO MONANGE 325ML DETOX TERAPIA</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>31179</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
-      </c>
-      <c r="E162" t="n">
-        <v>12</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G162" t="n">
-        <v>2</v>
-      </c>
-      <c r="H162" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>34753</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>SUCO DE UVA TREBOM PET 1 35L</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>34554</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
-        <v>6</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G163" t="n">
-        <v>144</v>
-      </c>
-      <c r="H163" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE FRUT PET 1 5L FRUT CITRICAS</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E164" t="n">
-        <v>6</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G164" t="n">
-        <v>136</v>
-      </c>
-      <c r="H164" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>3868</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE FRUT PET 1 5L LIMAO</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
-        <v>6</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G165" t="n">
-        <v>5</v>
-      </c>
-      <c r="H165" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>8523</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE FRUT PET 450ML LARANJA</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
-        <v>6</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G166" t="n">
-        <v>7</v>
-      </c>
-      <c r="H166" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE LT 290ML MANGA</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E167" t="n">
-        <v>6</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G167" t="n">
-        <v>5</v>
-      </c>
-      <c r="H167" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE LT 290ML PESSEGO</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>6</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G168" t="n">
-        <v>10</v>
-      </c>
-      <c r="H168" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE LT 290ML UVA</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E169" t="n">
-        <v>6</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G169" t="n">
-        <v>14</v>
-      </c>
-      <c r="H169" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE TP 1L ABACAXI</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E170" t="n">
-        <v>6</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G170" t="n">
-        <v>36</v>
-      </c>
-      <c r="H170" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE TP 1L MANGA</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E171" t="n">
-        <v>6</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G171" t="n">
-        <v>20</v>
-      </c>
-      <c r="H171" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE TP 1L PESSEGO</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E172" t="n">
-        <v>6</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G172" t="n">
-        <v>48</v>
-      </c>
-      <c r="H172" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE TP 1L UVA</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E173" t="n">
-        <v>6</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G173" t="n">
-        <v>33</v>
-      </c>
-      <c r="H173" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE TP 200ML PESSEGO</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
-        <v>18</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G174" t="n">
-        <v>30</v>
-      </c>
-      <c r="H174" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>SUCO DEL VALLE TP 200ML UVA</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>34479</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="E175" t="n">
-        <v>18</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G175" t="n">
-        <v>21</v>
-      </c>
-      <c r="H175" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>SUCO KAPO 200ML ABACAXI</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E176" t="n">
-        <v>12</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G176" t="n">
-        <v>70</v>
-      </c>
-      <c r="H176" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>SUCO KAPO 200ML LARANJA</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E177" t="n">
-        <v>12</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G177" t="n">
-        <v>236</v>
-      </c>
-      <c r="H177" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>SUCO KAPO 200ML UVA</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>34953</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E178" t="n">
-        <v>12</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G178" t="n">
-        <v>210</v>
-      </c>
-      <c r="H178" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>24807</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>TINGECOR GUARANY MARRON 40G</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>34479</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="E179" t="n">
-        <v>6</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G179" t="n">
-        <v>7</v>
-      </c>
-      <c r="H179" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>24808</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>TINGECOR GUARANY VERM 40G</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>34479</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="E180" t="n">
-        <v>6</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G180" t="n">
-        <v>10</v>
-      </c>
-      <c r="H180" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>24829</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>TINTURA BELAECOR 147G 8.0 LOURO CLARO</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>31179</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
-      </c>
-      <c r="E181" t="n">
-        <v>6</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G181" t="n">
-        <v>1</v>
-      </c>
-      <c r="H181" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>8666</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>TOALHA PISO ATLANTICA BASIC ROSA ROMA</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>36248</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E182" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G182" t="n">
-        <v>90</v>
-      </c>
-      <c r="H182" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>33288</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>TOALHA UMED SUPERFRAL ADULTO C 50 FLIPTOP</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>33234</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="E183" t="n">
-        <v>12</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G183" t="n">
-        <v>6</v>
-      </c>
-      <c r="H183" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>2471</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>TOMATE SECO CONSERVA JUREIA VD 200G</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E184" t="n">
-        <v>12</v>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G184" t="n">
-        <v>8</v>
-      </c>
-      <c r="H184" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>8714</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>VELA SANDERIANA BRANCA 265G</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E185" t="n">
-        <v>12</v>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G185" t="n">
-        <v>1</v>
-      </c>
-      <c r="H185" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>25406</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>VELA SANDERO C 8 N4 VM/BR</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E186" t="n">
-        <v>24</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G186" t="n">
-        <v>1</v>
-      </c>
-      <c r="H186" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>8722</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>VELA SANDERO N2 8UN 112G AZUL</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E187" t="n">
-        <v>24</v>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G187" t="n">
-        <v>3</v>
-      </c>
-      <c r="H187" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>8726</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>VELA SANDERO N4 8UN 144G ST SANTO EXPEDITO</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E188" t="n">
-        <v>24</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G188" t="n">
-        <v>3</v>
-      </c>
-      <c r="H188" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>25408</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>VELA SANDERO T 7 DIAS AZUL</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E189" t="n">
-        <v>12</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G189" t="n">
-        <v>4</v>
-      </c>
-      <c r="H189" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>25410</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>VELA SANDERO T 7 DIAS VERM</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E190" t="n">
-        <v>12</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G190" t="n">
-        <v>10</v>
-      </c>
-      <c r="H190" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>25412</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>VELA SENDERO N7 SAG CORAC M</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="E191" t="n">
-        <v>12</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G191" t="n">
-        <v>7</v>
-      </c>
-      <c r="H191" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>25425</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>VH CANCAO BORDO SUAVE 750ML SV</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>33234</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="E192" t="n">
-        <v>12</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G192" t="n">
-        <v>11</v>
-      </c>
-      <c r="H192" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>25433</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>VH CONCHA Y TORO RESERV CAB SUAVE 750ML</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>33234</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="E193" t="n">
-        <v>12</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G193" t="n">
-        <v>9</v>
-      </c>
-      <c r="H193" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>3782</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>VINAGRE MACA KOLLER 500ML</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>33234</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="E194" t="n">
-        <v>12</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G194" t="n">
-        <v>37</v>
-      </c>
-      <c r="H194" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>VODKA RAJSKA 1L</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>34554</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E195" t="n">
-        <v>12</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G195" t="n">
-        <v>49</v>
-      </c>
-      <c r="H195" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>33724</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>VODKA WE MIX VD 275ML MORANGO E KIWI</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>34554</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E196" t="n">
-        <v>6</v>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="G196" t="n">
-        <v>15</v>
-      </c>
-      <c r="H196" t="n">
         <v>1</v>
       </c>
     </row>
